--- a/polymercanon/Paper-Results/Excel/Same polymer many notations/Duration.xlsx
+++ b/polymercanon/Paper-Results/Excel/Same polymer many notations/Duration.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -474,11 +474,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -492,11 +492,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -510,11 +510,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -528,11 +528,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -546,11 +546,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -564,11 +564,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -582,11 +582,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -600,11 +600,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -618,11 +618,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -636,11 +636,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[H]OCCOCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -654,11 +654,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CC(=O)[&lt;1],[&gt;3]OCC(CO[&lt;2])CO[&lt;2],[&gt;2]C(=O)CC(=O)[&lt;3],[&gt;3]OCC(CO[&lt;1])CO[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -672,11 +672,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CC(=O)[&lt;1],[&gt;3]OCC(CO[&lt;2])CO[&lt;2],[&gt;2]C(=O)CC(=O)[&lt;3],[&gt;3]OCC(CO[&lt;1])CO[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -690,11 +690,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CC(=O)[&lt;1],[&gt;3]OCC(CO[&lt;2])CO[&lt;2],[&gt;2]C(=O)CC(=O)[&lt;3],[&gt;3]OCC(CO[&lt;1])CO[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -708,11 +708,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CC(=O)[&lt;1],[&gt;3]OCC(CO[&lt;2])CO[&lt;2],[&gt;2]C(=O)CC(=O)[&lt;3],[&gt;3]OCC(CO[&lt;1])CO[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -726,11 +726,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CC(=O)[&lt;1],[&gt;3]OCC(CO[&lt;2])CO[&lt;2],[&gt;2]C(=O)CC(=O)[&lt;3],[&gt;3]OCC(CO[&lt;1])CO[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -744,11 +744,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCO[&lt;][&gt;]}CCO{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -762,11 +762,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCO[&lt;][&gt;]}CCO{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -780,11 +780,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][&gt;]}OCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -798,11 +798,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}OCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -816,11 +816,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][&gt;]}OCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -834,11 +834,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCO[&lt;][&gt;]}CCO{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -852,11 +852,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCO[&lt;][&gt;]}CCO{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -870,11 +870,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)O)[&lt;],[&gt;]C(C(=O)O)C[&lt;],[&gt;]CC([&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}[H],[&gt;]C(C[&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}{[&lt;][&gt;]COC[&lt;][&gt;]}[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -888,11 +888,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)O)[&lt;],[&gt;]C(C(=O)O)C[&lt;],[&gt;]CC([&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}[H],[&gt;]C(C[&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}{[&lt;][&gt;]COC[&lt;][&gt;]}[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -906,11 +906,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)O)[&lt;],[&gt;]C(C(=O)O)C[&lt;],[&gt;]CC([&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}[H],[&gt;]C(C[&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}{[&lt;][&gt;]COC[&lt;][&gt;]}[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -924,11 +924,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)O)[&lt;],[&gt;]C(C(=O)O)C[&lt;],[&gt;]CC([&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}[H],[&gt;]C(C[&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}{[&lt;][&gt;]COC[&lt;][&gt;]}[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -942,11 +942,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -960,11 +960,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -978,11 +978,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -996,11 +996,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1014,11 +1014,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1032,11 +1032,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1050,11 +1050,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;],[&gt;]OC(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1104,11 +1104,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;],[&gt;]OC(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;],[&gt;]OC(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;],[&gt;]OC(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;],[&gt;]OC(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;],[&gt;]OC(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1302,11 +1302,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}CC(c(cc1)ccc1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}CC(c(cc1)ccc1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[H]C[Si](C)(C)O[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[H]C[Si](C)(C)O[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1392,11 +1392,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[H]C[Si](C)(C)O[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1410,11 +1410,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[H]C[Si](C)(C)O[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[H]C[Si](C)(C)O[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1446,11 +1446,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{[][&gt;]N=Cc(cc1)ccc1C=NCCC[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1464,11 +1464,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{[][&gt;]N=Cc(cc1)ccc1C=NCCC[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1482,11 +1482,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1500,11 +1500,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]COC[&lt;][&gt;]}C(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1536,11 +1536,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]COC[&lt;][&gt;]}C(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1554,11 +1554,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]COC[&lt;][&gt;]}C(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1572,11 +1572,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]COC[&lt;][&gt;]}C(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1590,11 +1590,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]COC[&lt;][&gt;]}C(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]COC[&lt;][&gt;]}C(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]COC[&lt;][&gt;]}C(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1644,11 +1644,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[H]C{[&lt;][&gt;]OCC[&lt;][&gt;]}n(nn4)cc4c(cc(c(nn1)cn1CC{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc8)ccc8)C[&lt;][&gt;]}CCC[H])c2)cc2CO{[&lt;][&gt;]C(=C)CCCCCO[&lt;][&gt;]}C(=O)CCCCCO[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -1662,11 +1662,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[H]C{[&lt;][&gt;]OCC[&lt;][&gt;]}n(nn4)cc4c(cc(c(nn1)cn1CC{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc8)ccc8)C[&lt;][&gt;]}CCC[H])c2)cc2CO{[&lt;][&gt;]C(=C)CCCCCO[&lt;][&gt;]}C(=O)CCCCCO[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -1680,11 +1680,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[H]C{[&lt;][&gt;]OCC[&lt;][&gt;]}n(nn4)cc4c(cc(c(nn1)cn1CC{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc8)ccc8)C[&lt;][&gt;]}CCC[H])c2)cc2CO{[&lt;][&gt;]C(=C)CCCCCO[&lt;][&gt;]}C(=O)CCCCCO[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[H]C{[&lt;][&gt;]OCC[&lt;][&gt;]}n(nn4)cc4c(cc(c(nn1)cn1CC{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc8)ccc8)C[&lt;][&gt;]}CCC[H])c2)cc2CO{[&lt;][&gt;]C(=C)CCCCCO[&lt;][&gt;]}C(=O)CCCCCO[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -1716,11 +1716,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[H]C{[&lt;][&gt;]OCC[&lt;][&gt;]}n(nn4)cc4c(cc(c(nn1)cn1CC{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc8)ccc8)C[&lt;][&gt;]}CCC[H])c2)cc2CO{[&lt;][&gt;]C(=C)CCCCCO[&lt;][&gt;]}C(=O)CCCCCO[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -1734,11 +1734,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Br{[&lt;][&gt;]CCO[&lt;][&gt;]}C(C)C(=O)OCC(C)(C(=O)O{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}C(=O)C(C)(COC(=O)C(C){[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}Br)COC(=O)C(C){[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}Br)COC(=O)C(C){[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>182</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -1752,11 +1752,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Br{[&lt;][&gt;]CCO[&lt;][&gt;]}C(C)C(=O)OCC(C)(C(=O)O{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}C(=O)C(C)(COC(=O)C(C){[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}Br)COC(=O)C(C){[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}Br)COC(=O)C(C){[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -1770,11 +1770,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][&gt;]}C(=O)CCN(CCN(CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1788,11 +1788,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][&gt;]}C(=O)CCN(CCN(CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1806,11 +1806,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][&gt;]}C(=O)CCN(CCN(CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1824,11 +1824,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(nn4)cn4[&lt;1],[&gt;3]COCC(COC[&lt;2])(COC[&lt;2])COC[&lt;2],[&gt;4]n(nn2)cc2[&lt;3],[&gt;2]c(nn1)cn1[&lt;6],[&gt;4]n(nn8)cc8[&lt;1],[&gt;3]COCC(COC[&lt;1])(COC[&lt;1])COC[&lt;1],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;4],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -1842,11 +1842,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(nn4)cn4[&lt;1],[&gt;3]COCC(COC[&lt;2])(COC[&lt;2])COC[&lt;2],[&gt;4]n(nn2)cc2[&lt;3],[&gt;2]c(nn1)cn1[&lt;6],[&gt;4]n(nn8)cc8[&lt;1],[&gt;3]COCC(COC[&lt;1])(COC[&lt;1])COC[&lt;1],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;4],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -1860,11 +1860,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(nn4)cn4[&lt;1],[&gt;3]COCC(COC[&lt;2])(COC[&lt;2])COC[&lt;2],[&gt;4]n(nn2)cc2[&lt;3],[&gt;2]c(nn1)cn1[&lt;6],[&gt;4]n(nn8)cc8[&lt;1],[&gt;3]COCC(COC[&lt;1])(COC[&lt;1])COC[&lt;1],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;4],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -1878,11 +1878,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][&gt;]}OCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1896,11 +1896,29 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][&gt;]}OCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>24</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>{[&gt;][&lt;]CCO[&gt;],[&lt;]CCO[&gt;2],[&lt;2]CC(c1ccccc1)[&gt;2],[&gt;2]CC(c1ccccc1)[&lt;2][&lt;2]}</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/polymercanon/Paper-Results/Excel/Same polymer many notations/Duration.xlsx
+++ b/polymercanon/Paper-Results/Excel/Same polymer many notations/Duration.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,11 +798,8 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
+          <t>[H]{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}OCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1900,24 +1897,6 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>{[&gt;][&lt;]CCO[&gt;],[&lt;]CCO[&gt;2],[&lt;2]CC(c1ccccc1)[&gt;2],[&gt;2]CC(c1ccccc1)[&lt;2][&lt;2]}</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
         <v>0</v>
       </c>
     </row>

--- a/polymercanon/Paper-Results/Excel/Same polymer many notations/Duration.xlsx
+++ b/polymercanon/Paper-Results/Excel/Same polymer many notations/Duration.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,6 +801,9 @@
           <t>[H]{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}OCC{[&lt;][&gt;]OCC[&lt;][&gt;]}[H]</t>
         </is>
       </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">

--- a/polymercanon/Paper-Results/Excel/Same polymer many notations/Duration.xlsx
+++ b/polymercanon/Paper-Results/Excel/Same polymer many notations/Duration.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.815608</v>
+        <v>2.650661</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.438447</v>
+        <v>2.699056</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.364666</v>
+        <v>2.680281</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.436447</v>
+        <v>2.735053</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.382187</v>
+        <v>3.098923</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.378047</v>
+        <v>2.895755</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.879044</v>
+        <v>2.652698</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.99224</v>
+        <v>2.722656</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.978604</v>
+        <v>2.706493</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.099834</v>
+        <v>2.807776</v>
       </c>
     </row>
     <row r="12">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.486601</v>
+        <v>5.390869</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.642639</v>
+        <v>2.845328</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.601059</v>
+        <v>2.879923</v>
       </c>
     </row>
     <row r="15">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.848487</v>
+        <v>2.940852</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.757627</v>
+        <v>2.82609</v>
       </c>
     </row>
     <row r="17">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.578364</v>
+        <v>2.738196</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.552445</v>
+        <v>4.923865</v>
       </c>
     </row>
     <row r="19">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.233932</v>
+        <v>4.951784</v>
       </c>
     </row>
     <row r="20">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.634911</v>
+        <v>3.774412</v>
       </c>
     </row>
     <row r="21">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.72315</v>
+        <v>2.347182</v>
       </c>
     </row>
     <row r="22">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.675122</v>
+        <v>3.775373</v>
       </c>
     </row>
     <row r="23">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.99699</v>
+        <v>2.434194</v>
       </c>
     </row>
     <row r="24">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10.639312</v>
+        <v>7.049043</v>
       </c>
     </row>
     <row r="25">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.885371</v>
+        <v>1.09123</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.597916</v>
+        <v>1.377262</v>
       </c>
     </row>
     <row r="27">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.183583</v>
+        <v>1.59612</v>
       </c>
     </row>
     <row r="28">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.403778</v>
+        <v>3.127162</v>
       </c>
     </row>
     <row r="29">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.937347</v>
+        <v>0.91625</v>
       </c>
     </row>
     <row r="30">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.079887</v>
+        <v>0.90942</v>
       </c>
     </row>
     <row r="31">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.156225</v>
+        <v>0.963697</v>
       </c>
     </row>
     <row r="32">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.977258</v>
+        <v>0.997362</v>
       </c>
     </row>
     <row r="33">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.8306829999999999</v>
+        <v>0.956828</v>
       </c>
     </row>
     <row r="34">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.891181</v>
+        <v>0.959326</v>
       </c>
     </row>
     <row r="35">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.011271</v>
+        <v>0.9627250000000001</v>
       </c>
     </row>
     <row r="36">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.954029</v>
+        <v>1.910814</v>
       </c>
     </row>
     <row r="37">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.701405</v>
+        <v>2.060703</v>
       </c>
     </row>
     <row r="38">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.0442</v>
+        <v>2.101889</v>
       </c>
     </row>
     <row r="39">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.691733</v>
+        <v>2.210311</v>
       </c>
     </row>
     <row r="40">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.912839</v>
+        <v>2.300662</v>
       </c>
     </row>
     <row r="41">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2.591712</v>
+        <v>2.183505</v>
       </c>
     </row>
     <row r="42">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.664492</v>
+        <v>2.072262</v>
       </c>
     </row>
     <row r="43">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.087826</v>
+        <v>0.9240080000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.045153</v>
+        <v>0.9193789999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.110847</v>
+        <v>0.963849</v>
       </c>
     </row>
     <row r="46">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.147523</v>
+        <v>1.827926</v>
       </c>
     </row>
     <row r="47">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.14105</v>
+        <v>1.79535</v>
       </c>
     </row>
     <row r="48">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.040262</v>
+        <v>1.82258</v>
       </c>
     </row>
     <row r="49">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.024993</v>
+        <v>1.605661</v>
       </c>
     </row>
     <row r="50">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.591497</v>
+        <v>1.976062</v>
       </c>
     </row>
     <row r="51">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.661439</v>
+        <v>2.144193</v>
       </c>
     </row>
     <row r="52">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.972878</v>
+        <v>1.929869</v>
       </c>
     </row>
     <row r="53">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3.074</v>
+        <v>2.428444</v>
       </c>
     </row>
     <row r="54">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3.022859</v>
+        <v>2.136012</v>
       </c>
     </row>
     <row r="55">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3.074126</v>
+        <v>2.904748</v>
       </c>
     </row>
     <row r="56">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3.013353</v>
+        <v>2.731985</v>
       </c>
     </row>
     <row r="57">
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.704051</v>
+        <v>2.429964</v>
       </c>
     </row>
     <row r="58">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.796228</v>
+        <v>3.104437</v>
       </c>
     </row>
     <row r="59">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.096155</v>
+        <v>1.035801</v>
       </c>
     </row>
     <row r="60">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.303571</v>
+        <v>1.046946</v>
       </c>
     </row>
     <row r="61">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7.435781</v>
+        <v>6.571522</v>
       </c>
     </row>
     <row r="62">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7.795078</v>
+        <v>6.056156</v>
       </c>
     </row>
     <row r="63">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7.371455</v>
+        <v>6.811394</v>
       </c>
     </row>
     <row r="64">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8.737048</v>
+        <v>6.687362</v>
       </c>
     </row>
     <row r="65">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7.611073</v>
+        <v>6.962253</v>
       </c>
     </row>
     <row r="66">
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17.582524</v>
+        <v>19.555081</v>
       </c>
     </row>
     <row r="67">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8.052716</v>
+        <v>7.858687</v>
       </c>
     </row>
     <row r="68">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>15.674562</v>
+        <v>14.315687</v>
       </c>
     </row>
     <row r="69">
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>15.659137</v>
+        <v>15.124834</v>
       </c>
     </row>
     <row r="70">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>21.348157</v>
+        <v>14.409957</v>
       </c>
     </row>
     <row r="71">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>16.94785</v>
+        <v>14.479454</v>
       </c>
     </row>
     <row r="72">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>19.025717</v>
+        <v>14.59024</v>
       </c>
     </row>
     <row r="73">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>37.660655</v>
+        <v>32.766332</v>
       </c>
     </row>
     <row r="74">
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>12.754563</v>
+        <v>11.978846</v>
       </c>
     </row>
     <row r="75">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4.291071</v>
+        <v>3.929227</v>
       </c>
     </row>
     <row r="76">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4.121182</v>
+        <v>4.025075</v>
       </c>
     </row>
     <row r="77">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4.0853</v>
+        <v>4.001628</v>
       </c>
     </row>
     <row r="78">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6.657051</v>
+        <v>5.794624</v>
       </c>
     </row>
     <row r="79">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9.497525</v>
+        <v>5.739054</v>
       </c>
     </row>
     <row r="80">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5.940572</v>
+        <v>5.644974</v>
       </c>
     </row>
     <row r="81">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2.499521</v>
+        <v>2.37058</v>
       </c>
     </row>
     <row r="82">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4.23924</v>
+        <v>3.66329</v>
       </c>
     </row>
   </sheetData>
